--- a/src/main/resources/Create_Case.xlsx
+++ b/src/main/resources/Create_Case.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A0D1E2D-1B4B-41E0-93D2-038C8723CE1F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E8D961-713B-43AE-9489-FC30387D77D4}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
+    <sheet name="Creation1" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="13">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -56,6 +57,9 @@
   </si>
   <si>
     <t>Record created to test cases through automation</t>
+  </si>
+  <si>
+    <t>Medium</t>
   </si>
 </sst>
 </file>
@@ -503,4 +507,107 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA0D96E9-7BAF-4F04-9D97-EBE9A8544BC1}">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C8" s="3"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="4"/>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="4"/>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="4"/>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="4"/>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="4"/>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="4"/>
+      <c r="C15" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>